--- a/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/TORNILLO PUNTA AGUJA WAFER DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/TORNILLO PUNTA AGUJA WAFER DISMAY.xlsx
@@ -987,14 +987,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45216.53898003436</v>
+        <v>45266</v>
       </c>
       <c r="F1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="37">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1052,16 +1048,6 @@
       <c r="G11" s="26" t="n"/>
       <c r="H11" s="26" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="13.5" customHeight="1" s="37" thickBot="1"/>
     <row r="23">
       <c r="A23" s="16" t="n"/>
@@ -1107,7 +1093,7 @@
       </c>
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="30" t="n">
-        <v>725.1</v>
+        <v>599.26</v>
       </c>
       <c r="E25" s="23" t="n">
         <v>100</v>
@@ -1148,7 +1134,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="37">
       <c r="A32" s="39" t="n"/>
       <c r="B32" s="39" t="n"/>
@@ -1161,21 +1146,15 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" s="37"/>
     <row r="35" ht="16.5" customHeight="1" s="37"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="37">
       <c r="A39" s="6" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="4" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="5" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1185,11 +1164,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A29:E29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
